--- a/AAII_Financials/Quarterly/BAOS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAOS_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/BAOS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAOS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="92">
   <si>
     <t>BAOS</t>
   </si>
@@ -656,53 +656,54 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
@@ -721,29 +722,32 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2400</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
@@ -762,8 +766,11 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -771,20 +778,20 @@
         <v>300</v>
       </c>
       <c r="E9" s="3">
+        <v>300</v>
+      </c>
+      <c r="F9" s="3">
         <v>1000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1000</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
@@ -803,29 +810,32 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>600</v>
+      </c>
+      <c r="E10" s="3">
         <v>1200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-1100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1400</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
@@ -844,8 +854,11 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -861,8 +874,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -902,8 +916,11 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -943,26 +960,29 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>400</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -978,14 +998,17 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1025,8 +1048,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1039,29 +1065,30 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E17" s="3">
         <v>2100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>19500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4700</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1080,29 +1107,32 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-17500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-7200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2300</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1121,8 +1151,11 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1138,8 +1171,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1147,20 +1181,20 @@
         <v>600</v>
       </c>
       <c r="E20" s="3">
+        <v>600</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2000</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1179,23 +1213,26 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E21" s="3">
         <v>200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-17400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5900</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1220,8 +1257,11 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1261,29 +1301,32 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
         <v>-17400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-6500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-300</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1302,8 +1345,11 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1322,8 +1368,8 @@
       <c r="H24" s="3">
         <v>0</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
@@ -1334,8 +1380,8 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1343,8 +1389,11 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1384,29 +1433,32 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>-17400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-300</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1425,29 +1477,32 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>-17400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-300</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1466,8 +1521,11 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1507,8 +1565,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1548,8 +1609,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1589,8 +1653,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1630,8 +1697,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1639,20 +1709,20 @@
         <v>-600</v>
       </c>
       <c r="E32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2000</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1671,29 +1741,32 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>-17400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-300</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1712,8 +1785,11 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1753,29 +1829,32 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>-17400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-300</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1794,34 +1873,37 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1840,8 +1922,11 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1857,8 +1942,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1874,29 +1960,30 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E41" s="3">
         <v>3700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12100</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1915,29 +2002,32 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E42" s="3">
         <v>5100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3000</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1956,29 +2046,32 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E43" s="3">
         <v>30900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>32100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>51100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>58100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>56600</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1997,8 +2090,11 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2038,29 +2134,32 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E45" s="3">
         <v>1800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>20700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>26200</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2079,29 +2178,32 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E46" s="3">
         <v>41500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>50100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>71100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>86200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>98000</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2120,8 +2222,11 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2129,20 +2234,20 @@
         <v>6800</v>
       </c>
       <c r="E47" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F47" s="3">
         <v>2300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1500</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2161,8 +2266,11 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2170,19 +2278,19 @@
         <v>2100</v>
       </c>
       <c r="E48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F48" s="3">
         <v>2400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1900</v>
-      </c>
-      <c r="G48" s="3">
-        <v>2600</v>
       </c>
       <c r="H48" s="3">
         <v>2600</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
+      <c r="I48" s="3">
+        <v>2600</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
@@ -2202,28 +2310,31 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>400</v>
+      </c>
+      <c r="E49" s="3">
         <v>500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>700</v>
-      </c>
-      <c r="G49" s="3">
-        <v>800</v>
       </c>
       <c r="H49" s="3">
         <v>800</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
+      <c r="I49" s="3">
+        <v>800</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
@@ -2243,8 +2354,11 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2284,8 +2398,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2325,29 +2442,32 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
         <v>2600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2900</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2366,8 +2486,11 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2407,29 +2530,32 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E54" s="3">
         <v>53600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>58000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>77800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>94100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>105900</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2448,8 +2574,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2465,8 +2594,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2482,29 +2612,30 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E57" s="3">
         <v>7000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16700</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2523,28 +2654,31 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1500</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
@@ -2564,8 +2698,11 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2573,20 +2710,20 @@
         <v>1900</v>
       </c>
       <c r="E59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F59" s="3">
         <v>2300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8600</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2605,29 +2742,32 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E60" s="3">
         <v>10300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>25300</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2646,8 +2786,11 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2687,29 +2830,32 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
         <v>300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>800</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2728,8 +2874,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2769,8 +2918,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2810,8 +2962,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2851,29 +3006,32 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E66" s="3">
         <v>10300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>20000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>26100</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2892,8 +3050,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2909,8 +3070,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2950,8 +3112,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2991,8 +3156,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3032,8 +3200,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3073,29 +3244,32 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>6200</v>
+        <v>4300</v>
       </c>
       <c r="E72" s="3">
         <v>6200</v>
       </c>
       <c r="F72" s="3">
+        <v>6200</v>
+      </c>
+      <c r="G72" s="3">
         <v>23600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>29900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>36400</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3114,8 +3288,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3155,8 +3332,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3196,8 +3376,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3237,29 +3420,32 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E76" s="3">
         <v>43300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>45400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>64200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>74100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>79800</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3278,8 +3464,11 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3319,34 +3508,37 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3365,29 +3557,32 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>-17400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-300</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3406,8 +3601,11 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3423,23 +3621,24 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>400</v>
+      </c>
+      <c r="E83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
       <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
         <v>400</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3455,8 +3654,8 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -3464,8 +3663,11 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3505,8 +3707,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3546,8 +3751,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3587,8 +3795,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3628,8 +3839,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3669,29 +3883,32 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E89" s="3">
         <v>2600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-27800</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3710,8 +3927,11 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3727,8 +3947,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3736,17 +3957,17 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1500</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-700</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
@@ -3756,8 +3977,8 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
+      <c r="L91" s="3">
+        <v>0</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
@@ -3768,8 +3989,11 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3809,8 +4033,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3850,29 +4077,32 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5700</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3891,8 +4121,11 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3908,8 +4141,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3949,8 +4183,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3990,8 +4227,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4031,8 +4271,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4072,29 +4315,32 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>1600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>38500</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4113,8 +4359,11 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4122,20 +4371,20 @@
         <v>-200</v>
       </c>
       <c r="E101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>700</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4154,29 +4403,32 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5700</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4193,6 +4445,9 @@
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BAOS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAOS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="92">
   <si>
     <t>BAOS</t>
   </si>
@@ -656,60 +656,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -725,35 +726,41 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
-        <v>900</v>
+      <c r="D8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E8" s="3">
-        <v>1500</v>
-      </c>
-      <c r="F8" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G8" s="3">
-        <v>400</v>
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H8" s="3">
-        <v>1500</v>
+        <v>100</v>
       </c>
       <c r="I8" s="3">
+        <v>100</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K8" s="3">
         <v>2400</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -769,35 +776,41 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E9" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>100</v>
+      </c>
+      <c r="I9" s="3">
+        <v>100</v>
+      </c>
+      <c r="J9" s="3">
+        <v>500</v>
+      </c>
+      <c r="K9" s="3">
         <v>1000</v>
       </c>
-      <c r="G9" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -813,35 +826,41 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>600</v>
+        <v>-100</v>
       </c>
       <c r="E10" s="3">
-        <v>1200</v>
+        <v>-100</v>
       </c>
       <c r="F10" s="3">
-        <v>1000</v>
+        <v>-300</v>
       </c>
       <c r="G10" s="3">
-        <v>-1100</v>
+        <v>-300</v>
       </c>
       <c r="H10" s="3">
-        <v>400</v>
+        <v>-100</v>
       </c>
       <c r="I10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>500</v>
+      </c>
+      <c r="K10" s="3">
         <v>1400</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -857,8 +876,14 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,8 +900,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -919,8 +946,14 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,31 +996,37 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>100</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-100</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>400</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -1001,37 +1040,43 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1051,8 +1096,14 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1066,35 +1117,37 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3400</v>
+        <v>800</v>
       </c>
       <c r="E17" s="3">
-        <v>2100</v>
+        <v>800</v>
       </c>
       <c r="F17" s="3">
-        <v>19500</v>
+        <v>600</v>
       </c>
       <c r="G17" s="3">
-        <v>7000</v>
+        <v>600</v>
       </c>
       <c r="H17" s="3">
-        <v>8700</v>
+        <v>400</v>
       </c>
       <c r="I17" s="3">
+        <v>400</v>
+      </c>
+      <c r="J17" s="3">
+        <v>9800</v>
+      </c>
+      <c r="K17" s="3">
         <v>4700</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1110,35 +1163,41 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-2500</v>
+        <v>-700</v>
       </c>
       <c r="E18" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="F18" s="3">
-        <v>-17500</v>
+        <v>-900</v>
       </c>
       <c r="G18" s="3">
-        <v>-6600</v>
+        <v>-900</v>
       </c>
       <c r="H18" s="3">
-        <v>-7200</v>
+        <v>-300</v>
       </c>
       <c r="I18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="K18" s="3">
         <v>-2300</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1154,8 +1213,14 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1172,35 +1237,37 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="F20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K20" s="3">
         <v>2000</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1216,31 +1283,37 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1500</v>
+        <v>-900</v>
       </c>
       <c r="E21" s="3">
-        <v>200</v>
+        <v>-900</v>
       </c>
       <c r="F21" s="3">
-        <v>-17400</v>
+        <v>-800</v>
       </c>
       <c r="G21" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-800</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-8600</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1260,8 +1333,14 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1283,8 +1362,8 @@
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1304,35 +1383,41 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-1800</v>
+        <v>-900</v>
       </c>
       <c r="E23" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="F23" s="3">
-        <v>-17400</v>
+        <v>-900</v>
       </c>
       <c r="G23" s="3">
-        <v>-6300</v>
+        <v>-900</v>
       </c>
       <c r="H23" s="3">
-        <v>-6500</v>
+        <v>0</v>
       </c>
       <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="K23" s="3">
         <v>-300</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1348,34 +1433,40 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
@@ -1383,17 +1474,23 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1436,35 +1533,41 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-1800</v>
+        <v>-900</v>
       </c>
       <c r="E26" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="F26" s="3">
-        <v>-17400</v>
+        <v>-900</v>
       </c>
       <c r="G26" s="3">
-        <v>-6300</v>
+        <v>-900</v>
       </c>
       <c r="H26" s="3">
-        <v>-6500</v>
+        <v>0</v>
       </c>
       <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="K26" s="3">
         <v>-300</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1480,35 +1583,41 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-1800</v>
+        <v>-900</v>
       </c>
       <c r="E27" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="F27" s="3">
-        <v>-17400</v>
+        <v>-900</v>
       </c>
       <c r="G27" s="3">
-        <v>-6300</v>
+        <v>-900</v>
       </c>
       <c r="H27" s="3">
-        <v>-6500</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="K27" s="3">
         <v>-300</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1524,8 +1633,14 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1568,8 +1683,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1612,8 +1733,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1656,8 +1783,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1700,35 +1833,41 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-600</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
-        <v>-600</v>
+        <v>-200</v>
       </c>
       <c r="F32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2000</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1744,35 +1883,41 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-1800</v>
+        <v>-900</v>
       </c>
       <c r="E33" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="F33" s="3">
-        <v>-17400</v>
+        <v>-900</v>
       </c>
       <c r="G33" s="3">
-        <v>-6300</v>
+        <v>-900</v>
       </c>
       <c r="H33" s="3">
-        <v>-6500</v>
+        <v>0</v>
       </c>
       <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="K33" s="3">
         <v>-300</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1788,8 +1933,14 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1832,35 +1983,41 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-1800</v>
+        <v>-900</v>
       </c>
       <c r="E35" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="F35" s="3">
-        <v>-17400</v>
+        <v>-900</v>
       </c>
       <c r="G35" s="3">
-        <v>-6300</v>
+        <v>-900</v>
       </c>
       <c r="H35" s="3">
-        <v>-6500</v>
+        <v>0</v>
       </c>
       <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="K35" s="3">
         <v>-300</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1876,40 +2033,46 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1925,8 +2088,14 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1943,8 +2112,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1961,35 +2132,37 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F41" s="3">
         <v>3300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
+        <v>3300</v>
+      </c>
+      <c r="H41" s="3">
         <v>3700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J41" s="3">
         <v>6700</v>
       </c>
-      <c r="G41" s="3">
-        <v>5000</v>
-      </c>
-      <c r="H41" s="3">
-        <v>4800</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>12100</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2005,35 +2178,41 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>3300</v>
+        <v>1800</v>
       </c>
       <c r="E42" s="3">
-        <v>5100</v>
+        <v>1800</v>
       </c>
       <c r="F42" s="3">
-        <v>4500</v>
+        <v>2600</v>
       </c>
       <c r="G42" s="3">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="H42" s="3">
-        <v>2700</v>
+        <v>4000</v>
       </c>
       <c r="I42" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J42" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K42" s="3">
         <v>3000</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2049,35 +2228,41 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>29200</v>
+      </c>
+      <c r="F43" s="3">
         <v>28700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
+        <v>28700</v>
+      </c>
+      <c r="H43" s="3">
         <v>30900</v>
       </c>
-      <c r="F43" s="3">
-        <v>32100</v>
-      </c>
-      <c r="G43" s="3">
-        <v>51100</v>
-      </c>
-      <c r="H43" s="3">
-        <v>58100</v>
-      </c>
       <c r="I43" s="3">
+        <v>30900</v>
+      </c>
+      <c r="J43" s="3">
+        <v>34800</v>
+      </c>
+      <c r="K43" s="3">
         <v>56600</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2093,31 +2278,37 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2137,35 +2328,41 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4200</v>
+        <v>4500</v>
       </c>
       <c r="E45" s="3">
-        <v>1800</v>
+        <v>4500</v>
       </c>
       <c r="F45" s="3">
-        <v>6900</v>
+        <v>5000</v>
       </c>
       <c r="G45" s="3">
-        <v>12300</v>
+        <v>5000</v>
       </c>
       <c r="H45" s="3">
-        <v>20700</v>
+        <v>3000</v>
       </c>
       <c r="I45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J45" s="3">
+        <v>5600</v>
+      </c>
+      <c r="K45" s="3">
         <v>26200</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2181,35 +2378,41 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>38400</v>
+      </c>
+      <c r="F46" s="3">
         <v>39500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
+        <v>39500</v>
+      </c>
+      <c r="H46" s="3">
         <v>41500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
+        <v>41500</v>
+      </c>
+      <c r="J46" s="3">
         <v>50100</v>
       </c>
-      <c r="G46" s="3">
-        <v>71100</v>
-      </c>
-      <c r="H46" s="3">
-        <v>86200</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>98000</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2225,35 +2428,41 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>6600</v>
+      </c>
+      <c r="F47" s="3">
         <v>6800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>6800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
+        <v>6800</v>
+      </c>
+      <c r="I47" s="3">
+        <v>6800</v>
+      </c>
+      <c r="J47" s="3">
         <v>2300</v>
       </c>
-      <c r="G47" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H47" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>1500</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2269,35 +2478,41 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F48" s="3">
         <v>2100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J48" s="3">
         <v>2400</v>
       </c>
-      <c r="G48" s="3">
-        <v>1900</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
         <v>2600</v>
       </c>
-      <c r="I48" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2313,35 +2528,41 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>300</v>
+      </c>
+      <c r="F49" s="3">
         <v>400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
+        <v>400</v>
+      </c>
+      <c r="H49" s="3">
         <v>500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="I49" s="3">
+        <v>500</v>
+      </c>
+      <c r="J49" s="3">
         <v>600</v>
       </c>
-      <c r="G49" s="3">
-        <v>700</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="K49" s="3">
         <v>800</v>
       </c>
-      <c r="I49" s="3">
-        <v>800</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2357,8 +2578,14 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2401,8 +2628,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2445,35 +2678,41 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3">
         <v>2600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="I52" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J52" s="3">
         <v>2700</v>
       </c>
-      <c r="G52" s="3">
-        <v>2800</v>
-      </c>
-      <c r="H52" s="3">
-        <v>3000</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2900</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2489,8 +2728,14 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2533,35 +2778,41 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>47200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>47200</v>
+      </c>
+      <c r="F54" s="3">
         <v>48800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
+        <v>48800</v>
+      </c>
+      <c r="H54" s="3">
         <v>53600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
+        <v>53600</v>
+      </c>
+      <c r="J54" s="3">
         <v>58000</v>
       </c>
-      <c r="G54" s="3">
-        <v>77800</v>
-      </c>
-      <c r="H54" s="3">
-        <v>94100</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>105900</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2577,8 +2828,14 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2595,8 +2852,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2613,35 +2872,37 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F57" s="3">
         <v>2300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H57" s="3">
         <v>7000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="I57" s="3">
+        <v>7000</v>
+      </c>
+      <c r="J57" s="3">
         <v>8900</v>
       </c>
-      <c r="G57" s="3">
-        <v>10400</v>
-      </c>
-      <c r="H57" s="3">
-        <v>12200</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>16700</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2657,34 +2918,40 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F58" s="3">
         <v>2300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H58" s="3">
         <v>1400</v>
       </c>
-      <c r="F58" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+        <v>1400</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -2701,35 +2968,41 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1900</v>
+        <v>1200</v>
       </c>
       <c r="E59" s="3">
-        <v>1900</v>
+        <v>1200</v>
       </c>
       <c r="F59" s="3">
-        <v>2300</v>
+        <v>1200</v>
       </c>
       <c r="G59" s="3">
-        <v>2900</v>
+        <v>1200</v>
       </c>
       <c r="H59" s="3">
-        <v>7300</v>
+        <v>1400</v>
       </c>
       <c r="I59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K59" s="3">
         <v>8600</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2745,35 +3018,41 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F60" s="3">
         <v>6500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
+        <v>6500</v>
+      </c>
+      <c r="H60" s="3">
         <v>10300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
+        <v>10300</v>
+      </c>
+      <c r="J60" s="3">
         <v>12600</v>
       </c>
-      <c r="G60" s="3">
-        <v>13300</v>
-      </c>
-      <c r="H60" s="3">
-        <v>19500</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>25300</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2789,8 +3068,14 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2833,8 +3118,14 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2844,24 +3135,24 @@
       <c r="E62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>300</v>
-      </c>
-      <c r="H62" s="3">
-        <v>500</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>800</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2877,8 +3168,14 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2921,8 +3218,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2965,8 +3268,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3009,35 +3318,41 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F66" s="3">
         <v>6500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
+        <v>6500</v>
+      </c>
+      <c r="H66" s="3">
         <v>10300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
+        <v>10300</v>
+      </c>
+      <c r="J66" s="3">
         <v>12600</v>
       </c>
-      <c r="G66" s="3">
-        <v>13600</v>
-      </c>
-      <c r="H66" s="3">
-        <v>20000</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>26100</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3053,8 +3368,14 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3071,8 +3392,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3115,8 +3438,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3159,8 +3488,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3203,8 +3538,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3247,35 +3588,41 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F72" s="3">
         <v>4300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
+        <v>4300</v>
+      </c>
+      <c r="H72" s="3">
         <v>6200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="I72" s="3">
         <v>6200</v>
       </c>
-      <c r="G72" s="3">
-        <v>23600</v>
-      </c>
-      <c r="H72" s="3">
-        <v>29900</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
+        <v>6200</v>
+      </c>
+      <c r="K72" s="3">
         <v>36400</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3291,8 +3638,14 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3335,8 +3688,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3379,8 +3738,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3423,35 +3788,41 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>39700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>39700</v>
+      </c>
+      <c r="F76" s="3">
         <v>42400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
+        <v>42400</v>
+      </c>
+      <c r="H76" s="3">
         <v>43300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
+        <v>43300</v>
+      </c>
+      <c r="J76" s="3">
         <v>45400</v>
       </c>
-      <c r="G76" s="3">
-        <v>64200</v>
-      </c>
-      <c r="H76" s="3">
-        <v>74100</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>79800</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3467,8 +3838,14 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3511,40 +3888,46 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3560,35 +3943,41 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-1800</v>
+        <v>-900</v>
       </c>
       <c r="E81" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="F81" s="3">
-        <v>-17400</v>
+        <v>-900</v>
       </c>
       <c r="G81" s="3">
-        <v>-6300</v>
+        <v>-900</v>
       </c>
       <c r="H81" s="3">
-        <v>-6500</v>
+        <v>0</v>
       </c>
       <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="K81" s="3">
         <v>-300</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3604,8 +3993,14 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3622,31 +4017,33 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
+        <v>100</v>
+      </c>
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
       <c r="G83" s="3">
-        <v>400</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="H83" s="3">
+        <v>200</v>
+      </c>
+      <c r="I83" s="3">
+        <v>200</v>
+      </c>
+      <c r="J83" s="3">
+        <v>200</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3657,17 +4054,23 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3710,8 +4113,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3754,8 +4163,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3798,8 +4213,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3842,8 +4263,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3886,35 +4313,41 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2300</v>
+        <v>-600</v>
       </c>
       <c r="E89" s="3">
-        <v>2600</v>
+        <v>-600</v>
       </c>
       <c r="F89" s="3">
-        <v>5600</v>
+        <v>-200</v>
       </c>
       <c r="G89" s="3">
-        <v>-4000</v>
+        <v>-200</v>
       </c>
       <c r="H89" s="3">
-        <v>-3500</v>
+        <v>1300</v>
       </c>
       <c r="I89" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J89" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K89" s="3">
         <v>-27800</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3930,8 +4363,14 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3948,31 +4387,33 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F91" s="3">
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3980,11 +4421,11 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
@@ -3992,8 +4433,14 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4036,8 +4483,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4080,35 +4533,41 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-6300</v>
+        <v>500</v>
       </c>
       <c r="E94" s="3">
-        <v>-5400</v>
+        <v>500</v>
       </c>
       <c r="F94" s="3">
-        <v>-5500</v>
+        <v>-500</v>
       </c>
       <c r="G94" s="3">
-        <v>1700</v>
+        <v>-500</v>
       </c>
       <c r="H94" s="3">
-        <v>-700</v>
+        <v>-2700</v>
       </c>
       <c r="I94" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="K94" s="3">
         <v>-5700</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4124,8 +4583,14 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4142,31 +4607,33 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4186,8 +4653,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4230,8 +4703,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4274,8 +4753,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4318,35 +4803,41 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3">
+        <v>400</v>
+      </c>
+      <c r="G100" s="3">
+        <v>400</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>800</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>38500</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4362,35 +4853,41 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="F101" s="3">
         <v>-100</v>
       </c>
       <c r="G101" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="H101" s="3">
-        <v>-600</v>
+        <v>-100</v>
       </c>
       <c r="I101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K101" s="3">
         <v>700</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4406,35 +4903,41 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-3400</v>
+        <v>-200</v>
       </c>
       <c r="E102" s="3">
-        <v>-3000</v>
+        <v>-200</v>
       </c>
       <c r="F102" s="3">
-        <v>1600</v>
+        <v>-200</v>
       </c>
       <c r="G102" s="3">
-        <v>-3800</v>
+        <v>-200</v>
       </c>
       <c r="H102" s="3">
-        <v>-7100</v>
+        <v>-1500</v>
       </c>
       <c r="I102" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J102" s="3">
+        <v>800</v>
+      </c>
+      <c r="K102" s="3">
         <v>5700</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4448,6 +4951,12 @@
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BAOS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAOS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="92">
   <si>
     <t>BAOS</t>
   </si>
@@ -656,67 +656,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -732,41 +733,47 @@
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>300</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
       </c>
       <c r="H8" s="3">
+        <v>400</v>
+      </c>
+      <c r="I8" s="3">
+        <v>400</v>
+      </c>
+      <c r="J8" s="3">
         <v>100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>2400</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -782,8 +789,14 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -794,29 +807,29 @@
         <v>100</v>
       </c>
       <c r="F9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
         <v>100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1000</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -832,41 +845,47 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>200</v>
+      </c>
+      <c r="F10" s="3">
         <v>-100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-100</v>
       </c>
-      <c r="F10" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G10" s="3">
-        <v>-300</v>
-      </c>
       <c r="H10" s="3">
+        <v>400</v>
+      </c>
+      <c r="I10" s="3">
+        <v>400</v>
+      </c>
+      <c r="J10" s="3">
         <v>-100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1400</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -882,8 +901,14 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,8 +927,10 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -952,8 +979,14 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1002,8 +1035,14 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1014,25 +1053,25 @@
         <v>-100</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-300</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
@@ -1046,14 +1085,20 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1079,10 +1124,10 @@
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1102,8 +1147,14 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1119,41 +1170,43 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>12900</v>
+      </c>
+      <c r="F17" s="3">
         <v>800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>800</v>
       </c>
-      <c r="F17" s="3">
-        <v>600</v>
-      </c>
-      <c r="G17" s="3">
-        <v>600</v>
-      </c>
       <c r="H17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J17" s="3">
         <v>400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>9800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4700</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1169,41 +1222,47 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-8800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-2300</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1219,8 +1278,14 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1239,23 +1304,25 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
@@ -1263,17 +1330,17 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>2000</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1289,38 +1356,44 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-8600</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1339,16 +1412,22 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1362,14 +1441,14 @@
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1389,16 +1468,22 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-900</v>
+        <v>-12600</v>
       </c>
       <c r="E23" s="3">
-        <v>-900</v>
+        <v>-12600</v>
       </c>
       <c r="F23" s="3">
         <v>-900</v>
@@ -1407,23 +1492,23 @@
         <v>-900</v>
       </c>
       <c r="H23" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="I23" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
         <v>-8700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-300</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1439,8 +1524,14 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1462,17 +1553,17 @@
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
@@ -1480,17 +1571,23 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1539,16 +1636,22 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-900</v>
+        <v>-12600</v>
       </c>
       <c r="E26" s="3">
-        <v>-900</v>
+        <v>-12600</v>
       </c>
       <c r="F26" s="3">
         <v>-900</v>
@@ -1557,23 +1660,23 @@
         <v>-900</v>
       </c>
       <c r="H26" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="I26" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
         <v>-8700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-300</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1589,16 +1692,22 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-900</v>
+        <v>-12600</v>
       </c>
       <c r="E27" s="3">
-        <v>-900</v>
+        <v>-12600</v>
       </c>
       <c r="F27" s="3">
         <v>-900</v>
@@ -1607,23 +1716,23 @@
         <v>-900</v>
       </c>
       <c r="H27" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="I27" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
         <v>-8700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-300</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1639,8 +1748,14 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1689,8 +1804,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1739,8 +1860,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1789,8 +1916,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1839,23 +1972,29 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
@@ -1863,17 +2002,17 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-2000</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1889,16 +2028,22 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-900</v>
+        <v>-12600</v>
       </c>
       <c r="E33" s="3">
-        <v>-900</v>
+        <v>-12600</v>
       </c>
       <c r="F33" s="3">
         <v>-900</v>
@@ -1907,23 +2052,23 @@
         <v>-900</v>
       </c>
       <c r="H33" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="I33" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
         <v>-8700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-300</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1939,8 +2084,14 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1989,16 +2140,22 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-900</v>
+        <v>-12600</v>
       </c>
       <c r="E35" s="3">
-        <v>-900</v>
+        <v>-12600</v>
       </c>
       <c r="F35" s="3">
         <v>-900</v>
@@ -2007,23 +2164,23 @@
         <v>-900</v>
       </c>
       <c r="H35" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="I35" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
         <v>-8700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-300</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2039,46 +2196,52 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2094,8 +2257,14 @@
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2114,8 +2283,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2134,41 +2305,43 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F41" s="3">
         <v>2900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>3700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>6700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>12100</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2184,41 +2357,47 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F42" s="3">
         <v>1800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>2600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>2600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>4000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>4000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>3100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>3000</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2234,41 +2413,47 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F43" s="3">
         <v>29200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>29200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>28700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>28700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>30900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>30900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>34800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>56600</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2284,8 +2469,14 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2310,11 +2501,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2334,41 +2525,47 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F45" s="3">
         <v>4500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>4500</v>
       </c>
-      <c r="F45" s="3">
-        <v>5000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>5000</v>
-      </c>
       <c r="H45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J45" s="3">
         <v>3000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>5600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>26200</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2384,41 +2581,47 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>12700</v>
+      </c>
+      <c r="F46" s="3">
         <v>38400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>38400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>39500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>39500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>41500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>41500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>50100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>98000</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2434,8 +2637,14 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2446,10 +2655,10 @@
         <v>6600</v>
       </c>
       <c r="F47" s="3">
-        <v>6800</v>
+        <v>6600</v>
       </c>
       <c r="G47" s="3">
-        <v>6800</v>
+        <v>6600</v>
       </c>
       <c r="H47" s="3">
         <v>6800</v>
@@ -2458,17 +2667,17 @@
         <v>6800</v>
       </c>
       <c r="J47" s="3">
+        <v>6800</v>
+      </c>
+      <c r="K47" s="3">
+        <v>6800</v>
+      </c>
+      <c r="L47" s="3">
         <v>2300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1500</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2484,22 +2693,28 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F48" s="3">
         <v>1900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1900</v>
-      </c>
-      <c r="F48" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G48" s="3">
-        <v>2100</v>
       </c>
       <c r="H48" s="3">
         <v>2100</v>
@@ -2508,17 +2723,17 @@
         <v>2100</v>
       </c>
       <c r="J48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L48" s="3">
         <v>2400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2600</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2534,41 +2749,47 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>200</v>
+      </c>
+      <c r="F49" s="3">
         <v>300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>800</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2584,8 +2805,14 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2634,8 +2861,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2684,8 +2917,14 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2701,24 +2940,24 @@
       <c r="G52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3">
         <v>2600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>2700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>2900</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2734,8 +2973,14 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2784,41 +3029,47 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>21200</v>
+      </c>
+      <c r="F54" s="3">
         <v>47200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>47200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>48800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>48800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>53600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>53600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>58000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>105900</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2834,8 +3085,14 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2854,8 +3111,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2874,41 +3133,43 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F57" s="3">
         <v>3300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>7000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>7000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>8900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>16700</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2924,40 +3185,46 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>700</v>
+      </c>
+      <c r="F58" s="3">
         <v>2200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2300</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1400</v>
       </c>
       <c r="J58" s="3">
         <v>1400</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
+        <v>1400</v>
+      </c>
+      <c r="L58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
@@ -2974,16 +3241,22 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="E59" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="F59" s="3">
         <v>1200</v>
@@ -2992,23 +3265,23 @@
         <v>1200</v>
       </c>
       <c r="H59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J59" s="3">
         <v>1400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>8600</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3024,41 +3297,47 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F60" s="3">
         <v>7600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>7600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>6500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>10300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>10300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>12600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>25300</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3074,8 +3353,14 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3124,8 +3409,14 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3150,15 +3441,15 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>800</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3174,8 +3465,14 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3224,8 +3521,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3274,8 +3577,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3324,41 +3633,47 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F66" s="3">
         <v>7600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>7600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>6500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>6500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>10300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>10300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>12600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>26100</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3374,8 +3689,14 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3394,8 +3715,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3444,8 +3767,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3494,8 +3823,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3544,8 +3879,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3594,41 +3935,47 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="F72" s="3">
         <v>2600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>4300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>4300</v>
-      </c>
-      <c r="H72" s="3">
-        <v>6200</v>
-      </c>
-      <c r="I72" s="3">
-        <v>6200</v>
       </c>
       <c r="J72" s="3">
         <v>6200</v>
       </c>
       <c r="K72" s="3">
+        <v>6200</v>
+      </c>
+      <c r="L72" s="3">
+        <v>6200</v>
+      </c>
+      <c r="M72" s="3">
         <v>36400</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3644,8 +3991,14 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3694,8 +4047,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3744,8 +4103,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3794,41 +4159,47 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>14800</v>
+      </c>
+      <c r="F76" s="3">
         <v>39700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>39700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>42400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>42400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>43300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>43300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>45400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>79800</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3844,8 +4215,14 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3894,46 +4271,52 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3949,16 +4332,22 @@
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-900</v>
+        <v>-12600</v>
       </c>
       <c r="E81" s="3">
-        <v>-900</v>
+        <v>-12600</v>
       </c>
       <c r="F81" s="3">
         <v>-900</v>
@@ -3967,23 +4356,23 @@
         <v>-900</v>
       </c>
       <c r="H81" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="I81" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="J81" s="3">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3">
+        <v>0</v>
+      </c>
+      <c r="L81" s="3">
         <v>-8700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-300</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3999,8 +4388,14 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4019,8 +4414,10 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4031,10 +4428,10 @@
         <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
         <v>200</v>
@@ -4045,11 +4442,11 @@
       <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
+      <c r="K83" s="3">
+        <v>200</v>
+      </c>
+      <c r="L83" s="3">
+        <v>200</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
@@ -4060,17 +4457,23 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4119,8 +4522,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4169,8 +4578,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4219,8 +4634,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4269,8 +4690,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4319,41 +4746,47 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>2800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-27800</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4369,8 +4802,14 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4389,22 +4828,24 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -4413,25 +4854,25 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -4439,8 +4880,14 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4489,8 +4936,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4539,41 +4992,47 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>100</v>
+      </c>
+      <c r="F94" s="3">
         <v>500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-500</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-2700</v>
       </c>
       <c r="J94" s="3">
         <v>-2700</v>
       </c>
       <c r="K94" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="L94" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="M94" s="3">
         <v>-5700</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4589,8 +5048,14 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4609,8 +5074,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4635,11 +5102,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4659,8 +5126,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4709,8 +5182,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4759,8 +5238,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4809,41 +5294,47 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="D100" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>38500</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4859,16 +5350,22 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F101" s="3">
         <v>-100</v>
@@ -4883,17 +5380,17 @@
         <v>-100</v>
       </c>
       <c r="J101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>700</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4909,16 +5406,22 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-200</v>
+        <v>-700</v>
       </c>
       <c r="E102" s="3">
-        <v>-200</v>
+        <v>-700</v>
       </c>
       <c r="F102" s="3">
         <v>-200</v>
@@ -4927,23 +5430,23 @@
         <v>-200</v>
       </c>
       <c r="H102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J102" s="3">
         <v>-1500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>5700</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4957,6 +5460,12 @@
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BAOS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAOS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="92">
   <si>
     <t>BAOS</t>
   </si>
@@ -656,74 +656,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
@@ -739,47 +741,53 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>100</v>
+      </c>
+      <c r="F8" s="3">
         <v>300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>300</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
       <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
         <v>400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>2400</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -795,8 +803,14 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -813,29 +827,29 @@
         <v>100</v>
       </c>
       <c r="H9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
         <v>100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1000</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -851,47 +865,53 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>-100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>-100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>-100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1400</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -907,8 +927,14 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -929,8 +955,10 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -985,8 +1013,14 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1041,16 +1075,22 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3">
         <v>-100</v>
@@ -1059,25 +1099,25 @@
         <v>-100</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-300</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
@@ -1091,14 +1131,20 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1130,10 +1176,10 @@
         <v>100</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1153,8 +1199,14 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1172,47 +1224,49 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F17" s="3">
         <v>12900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>12900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>9800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4700</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1228,47 +1282,53 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-12600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-12600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-8800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-2300</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1284,8 +1344,14 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1306,8 +1372,10 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1318,17 +1386,17 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1336,17 +1404,17 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>2000</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1362,44 +1430,50 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-12600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-12600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-8600</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1418,23 +1492,29 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
@@ -1447,14 +1527,14 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1474,22 +1554,28 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-12600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-12600</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-900</v>
       </c>
       <c r="H23" s="3">
         <v>-900</v>
@@ -1498,23 +1584,23 @@
         <v>-900</v>
       </c>
       <c r="J23" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="K23" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
         <v>-8700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-300</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1530,8 +1616,14 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1559,17 +1651,17 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
@@ -1577,17 +1669,23 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1642,22 +1740,28 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-12600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-12600</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-900</v>
       </c>
       <c r="H26" s="3">
         <v>-900</v>
@@ -1666,23 +1770,23 @@
         <v>-900</v>
       </c>
       <c r="J26" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="K26" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
         <v>-8700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-300</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1698,22 +1802,28 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-12600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-12600</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-900</v>
       </c>
       <c r="H27" s="3">
         <v>-900</v>
@@ -1722,23 +1832,23 @@
         <v>-900</v>
       </c>
       <c r="J27" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="K27" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
         <v>-8700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-300</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1754,8 +1864,14 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1810,8 +1926,14 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1866,8 +1988,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1922,8 +2050,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1978,8 +2112,14 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1990,17 +2130,17 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -2008,17 +2148,17 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-2000</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2034,22 +2174,28 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-12600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-12600</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-900</v>
       </c>
       <c r="H33" s="3">
         <v>-900</v>
@@ -2058,23 +2204,23 @@
         <v>-900</v>
       </c>
       <c r="J33" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="K33" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
         <v>-8700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-300</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2090,8 +2236,14 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2146,22 +2298,28 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-12600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-12600</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-900</v>
       </c>
       <c r="H35" s="3">
         <v>-900</v>
@@ -2170,23 +2328,23 @@
         <v>-900</v>
       </c>
       <c r="J35" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="K35" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
         <v>-8700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-300</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2202,52 +2360,58 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2263,8 +2427,14 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2285,8 +2455,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2307,47 +2479,49 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F41" s="3">
         <v>1500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>3300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>6700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>12100</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2363,47 +2537,53 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>400</v>
+      </c>
+      <c r="E42" s="3">
+        <v>400</v>
+      </c>
+      <c r="F42" s="3">
         <v>1300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>1800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>1800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>2600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>2600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>4000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>4000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>3100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>3000</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2419,47 +2599,53 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F43" s="3">
         <v>5900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>5900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>29200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>29200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>28700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>28700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>30900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>30900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>34800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>56600</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2475,8 +2661,14 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2507,11 +2699,11 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -2531,47 +2723,53 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F45" s="3">
         <v>4000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>4000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>4500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>4500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>4900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>4900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>3000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>3000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>5600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>26200</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2587,47 +2785,53 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>11600</v>
+      </c>
+      <c r="F46" s="3">
         <v>12700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>12700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>38400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>38400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>39500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>39500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>41500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>41500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>50100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>98000</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2643,8 +2847,14 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2661,10 +2871,10 @@
         <v>6600</v>
       </c>
       <c r="H47" s="3">
-        <v>6800</v>
+        <v>6600</v>
       </c>
       <c r="I47" s="3">
-        <v>6800</v>
+        <v>6600</v>
       </c>
       <c r="J47" s="3">
         <v>6800</v>
@@ -2673,17 +2883,17 @@
         <v>6800</v>
       </c>
       <c r="L47" s="3">
+        <v>6800</v>
+      </c>
+      <c r="M47" s="3">
+        <v>6800</v>
+      </c>
+      <c r="N47" s="3">
         <v>2300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1500</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2699,8 +2909,14 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2711,16 +2927,16 @@
         <v>1700</v>
       </c>
       <c r="F48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H48" s="3">
         <v>1900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1900</v>
-      </c>
-      <c r="H48" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I48" s="3">
-        <v>2100</v>
       </c>
       <c r="J48" s="3">
         <v>2100</v>
@@ -2729,17 +2945,17 @@
         <v>2100</v>
       </c>
       <c r="L48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="M48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="N48" s="3">
         <v>2400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2600</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2755,8 +2971,14 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2767,35 +2989,35 @@
         <v>200</v>
       </c>
       <c r="F49" s="3">
+        <v>200</v>
+      </c>
+      <c r="G49" s="3">
+        <v>200</v>
+      </c>
+      <c r="H49" s="3">
         <v>300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>800</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2811,8 +3033,14 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2867,8 +3095,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2923,8 +3157,14 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2946,24 +3186,24 @@
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3">
         <v>2600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>2600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>2700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>2900</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2979,8 +3219,14 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3035,47 +3281,53 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>20100</v>
+      </c>
+      <c r="F54" s="3">
         <v>21200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>21200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>47200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>47200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>48800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>48800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>53600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>53600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>58000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>105900</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3091,8 +3343,14 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3113,8 +3371,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3135,47 +3395,49 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F57" s="3">
         <v>3600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>7000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>7000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>8900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>16700</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3191,46 +3453,52 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2300</v>
-      </c>
-      <c r="J58" s="3">
-        <v>1400</v>
-      </c>
-      <c r="K58" s="3">
-        <v>1400</v>
       </c>
       <c r="L58" s="3">
         <v>1400</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
+        <v>1400</v>
+      </c>
+      <c r="N58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
@@ -3247,22 +3515,28 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F59" s="3">
         <v>1300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1200</v>
       </c>
       <c r="H59" s="3">
         <v>1200</v>
@@ -3271,23 +3545,23 @@
         <v>1200</v>
       </c>
       <c r="J59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L59" s="3">
         <v>1400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>8600</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3303,47 +3577,53 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F60" s="3">
         <v>6400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>7600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>6500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>10300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>10300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>12600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>25300</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3359,8 +3639,14 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3415,8 +3701,14 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3447,15 +3739,15 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3">
         <v>800</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3471,8 +3763,14 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3527,8 +3825,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3583,8 +3887,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3639,47 +3949,53 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F66" s="3">
         <v>6400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>6400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>7600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>7600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>6500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>6500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>10300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>10300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>12600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>26100</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3695,8 +4011,14 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3717,8 +4039,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3773,8 +4097,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3829,8 +4159,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3885,8 +4221,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3941,47 +4283,53 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-22600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-22600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>2600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>2600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>4300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>4300</v>
-      </c>
-      <c r="J72" s="3">
-        <v>6200</v>
-      </c>
-      <c r="K72" s="3">
-        <v>6200</v>
       </c>
       <c r="L72" s="3">
         <v>6200</v>
       </c>
       <c r="M72" s="3">
+        <v>6200</v>
+      </c>
+      <c r="N72" s="3">
+        <v>6200</v>
+      </c>
+      <c r="O72" s="3">
         <v>36400</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3997,8 +4345,14 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4053,8 +4407,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4109,8 +4469,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4165,47 +4531,53 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>10900</v>
+      </c>
+      <c r="F76" s="3">
         <v>14800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>14800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>39700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>39700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>42400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>42400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>43300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>43300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>45400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>79800</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4221,8 +4593,14 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4277,52 +4655,58 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4338,22 +4722,28 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-12600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-12600</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-900</v>
       </c>
       <c r="H81" s="3">
         <v>-900</v>
@@ -4362,23 +4752,23 @@
         <v>-900</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="K81" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="L81" s="3">
+        <v>0</v>
+      </c>
+      <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
         <v>-8700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-300</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4394,8 +4784,14 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4416,8 +4812,10 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4434,10 +4832,10 @@
         <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
         <v>200</v>
@@ -4448,11 +4846,11 @@
       <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3">
+        <v>200</v>
+      </c>
+      <c r="N83" s="3">
+        <v>200</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
@@ -4463,17 +4861,23 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4528,8 +4932,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4584,8 +4994,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4640,8 +5056,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4696,8 +5118,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4752,47 +5180,53 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>2800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-27800</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4808,8 +5242,14 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4830,28 +5270,30 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -4860,25 +5302,25 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-800</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
@@ -4886,8 +5328,14 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4942,8 +5390,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4998,47 +5452,53 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>500</v>
+      </c>
+      <c r="F94" s="3">
         <v>100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-500</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-2700</v>
       </c>
       <c r="L94" s="3">
         <v>-2700</v>
       </c>
       <c r="M94" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="N94" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="O94" s="3">
         <v>-5700</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5054,8 +5514,14 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5076,8 +5542,10 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5108,11 +5576,11 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -5132,8 +5600,14 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5188,8 +5662,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5244,8 +5724,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5300,47 +5786,53 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F100" s="3">
         <v>-800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-800</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>38500</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5356,8 +5848,14 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5368,10 +5866,10 @@
         <v>0</v>
       </c>
       <c r="F101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H101" s="3">
         <v>-100</v>
@@ -5386,17 +5884,17 @@
         <v>-100</v>
       </c>
       <c r="L101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>700</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5412,22 +5910,28 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-700</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-200</v>
       </c>
       <c r="H102" s="3">
         <v>-200</v>
@@ -5436,23 +5940,23 @@
         <v>-200</v>
       </c>
       <c r="J102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L102" s="3">
         <v>-1500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>5700</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5466,6 +5970,12 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BAOS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAOS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="92">
   <si>
     <t>BAOS</t>
   </si>
@@ -656,82 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -747,8 +748,14 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -759,41 +766,41 @@
         <v>100</v>
       </c>
       <c r="F8" s="3">
+        <v>100</v>
+      </c>
+      <c r="G8" s="3">
+        <v>100</v>
+      </c>
+      <c r="H8" s="3">
         <v>300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>300</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
       <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
         <v>400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2400</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -809,8 +816,14 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -833,29 +846,29 @@
         <v>100</v>
       </c>
       <c r="J9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3">
         <v>100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1000</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -871,8 +884,14 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -883,41 +902,41 @@
         <v>0</v>
       </c>
       <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>-100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>-100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>-100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1400</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -933,8 +952,14 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -957,8 +982,10 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1019,8 +1046,14 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1081,22 +1114,28 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="F14" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3">
         <v>-100</v>
@@ -1105,25 +1144,25 @@
         <v>-100</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-300</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
@@ -1137,14 +1176,20 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1182,10 +1227,10 @@
         <v>100</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1205,8 +1250,14 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1226,53 +1277,55 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F17" s="3">
         <v>2300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>12900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>12900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>9800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>4700</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1288,53 +1341,59 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-2100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-12600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-12600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-8800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-2300</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1350,8 +1409,14 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1374,16 +1439,18 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1392,17 +1459,17 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1410,17 +1477,17 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>2000</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1436,50 +1503,56 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-2100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-12600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-12600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-8600</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1498,29 +1571,35 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
       <c r="J22" s="3">
         <v>0</v>
       </c>
@@ -1533,14 +1612,14 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1560,28 +1639,34 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-2100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-12600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-12600</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-900</v>
       </c>
       <c r="J23" s="3">
         <v>-900</v>
@@ -1590,23 +1675,23 @@
         <v>-900</v>
       </c>
       <c r="L23" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="M23" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
         <v>-8700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-300</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1622,16 +1707,22 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
@@ -1657,17 +1748,17 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
@@ -1675,17 +1766,23 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1746,28 +1843,34 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-2100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-12600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-12600</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-900</v>
       </c>
       <c r="J26" s="3">
         <v>-900</v>
@@ -1776,23 +1879,23 @@
         <v>-900</v>
       </c>
       <c r="L26" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="M26" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
         <v>-8700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-300</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,28 +1911,34 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-2100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-12600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-12600</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-900</v>
       </c>
       <c r="J27" s="3">
         <v>-900</v>
@@ -1838,23 +1947,23 @@
         <v>-900</v>
       </c>
       <c r="L27" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="M27" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
         <v>-8700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-300</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1870,8 +1979,14 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1932,8 +2047,14 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1994,8 +2115,14 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2056,8 +2183,14 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2118,16 +2251,22 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -2136,17 +2275,17 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -2154,17 +2293,17 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-2000</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2180,28 +2319,34 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-2100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-12600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-12600</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-900</v>
       </c>
       <c r="J33" s="3">
         <v>-900</v>
@@ -2210,23 +2355,23 @@
         <v>-900</v>
       </c>
       <c r="L33" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="M33" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
         <v>-8700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-300</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2242,8 +2387,14 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2304,28 +2455,34 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-2100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-12600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-12600</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-900</v>
       </c>
       <c r="J35" s="3">
         <v>-900</v>
@@ -2334,23 +2491,23 @@
         <v>-900</v>
       </c>
       <c r="L35" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="M35" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
         <v>-8700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-300</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2366,58 +2523,64 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2433,8 +2596,14 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2457,8 +2626,10 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2481,53 +2652,55 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F41" s="3">
         <v>1200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>6700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>12100</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2543,8 +2716,14 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2555,41 +2734,41 @@
         <v>400</v>
       </c>
       <c r="F42" s="3">
+        <v>400</v>
+      </c>
+      <c r="G42" s="3">
+        <v>400</v>
+      </c>
+      <c r="H42" s="3">
         <v>1300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>1300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>1800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>1800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>2600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>2600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>4000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>4000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>3100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>3000</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2605,53 +2784,59 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F43" s="3">
         <v>6400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>6400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>5900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>5900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>29200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>29200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>28700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>28700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>30900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>30900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>34800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>56600</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2667,8 +2852,14 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2705,11 +2896,11 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2729,53 +2920,59 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>600</v>
+      </c>
+      <c r="F45" s="3">
         <v>3600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>3600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>4000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>4000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>4500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>4500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>4900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>4900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>3000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>3000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>5600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>26200</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,53 +2988,59 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F46" s="3">
         <v>11600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>11600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>12700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>12700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>38400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>38400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>39500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>39500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>41500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>41500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>50100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>98000</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2853,16 +3056,22 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>6600</v>
+        <v>4800</v>
       </c>
       <c r="E47" s="3">
-        <v>6600</v>
+        <v>4800</v>
       </c>
       <c r="F47" s="3">
         <v>6600</v>
@@ -2877,10 +3086,10 @@
         <v>6600</v>
       </c>
       <c r="J47" s="3">
-        <v>6800</v>
+        <v>6600</v>
       </c>
       <c r="K47" s="3">
-        <v>6800</v>
+        <v>6600</v>
       </c>
       <c r="L47" s="3">
         <v>6800</v>
@@ -2889,17 +3098,17 @@
         <v>6800</v>
       </c>
       <c r="N47" s="3">
+        <v>6800</v>
+      </c>
+      <c r="O47" s="3">
+        <v>6800</v>
+      </c>
+      <c r="P47" s="3">
         <v>2300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1500</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2915,16 +3124,22 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1700</v>
+        <v>700</v>
       </c>
       <c r="E48" s="3">
-        <v>1700</v>
+        <v>700</v>
       </c>
       <c r="F48" s="3">
         <v>1700</v>
@@ -2933,16 +3148,16 @@
         <v>1700</v>
       </c>
       <c r="H48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J48" s="3">
         <v>1900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1900</v>
-      </c>
-      <c r="J48" s="3">
-        <v>2100</v>
-      </c>
-      <c r="K48" s="3">
-        <v>2100</v>
       </c>
       <c r="L48" s="3">
         <v>2100</v>
@@ -2951,17 +3166,17 @@
         <v>2100</v>
       </c>
       <c r="N48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="O48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="P48" s="3">
         <v>2400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2600</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2977,16 +3192,22 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>200</v>
@@ -2995,35 +3216,35 @@
         <v>200</v>
       </c>
       <c r="H49" s="3">
+        <v>200</v>
+      </c>
+      <c r="I49" s="3">
+        <v>200</v>
+      </c>
+      <c r="J49" s="3">
         <v>300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>800</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3039,8 +3260,14 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3101,8 +3328,14 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3163,8 +3396,14 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3192,24 +3431,24 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3">
         <v>2600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>2600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>2700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>2900</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3225,8 +3464,14 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3287,53 +3532,59 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>12400</v>
+      </c>
+      <c r="F54" s="3">
         <v>20100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>20100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>21200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>21200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>47200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>47200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>48800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>48800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>53600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>53600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>58000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>105900</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,8 +3600,14 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3373,8 +3630,10 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3397,53 +3656,55 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F57" s="3">
         <v>7000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>7000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>3300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>7000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>7000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>8900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>16700</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3459,52 +3720,58 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2300</v>
-      </c>
-      <c r="L58" s="3">
-        <v>1400</v>
-      </c>
-      <c r="M58" s="3">
-        <v>1400</v>
       </c>
       <c r="N58" s="3">
         <v>1400</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
+        <v>1400</v>
+      </c>
+      <c r="P58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
@@ -3521,28 +3788,34 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F59" s="3">
         <v>1400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1300</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1200</v>
       </c>
       <c r="J59" s="3">
         <v>1200</v>
@@ -3551,23 +3824,23 @@
         <v>1200</v>
       </c>
       <c r="L59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N59" s="3">
         <v>1400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>8600</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3583,53 +3856,59 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F60" s="3">
         <v>9200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>9200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>6400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>7600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>7600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>6500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>6500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>10300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>10300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>12600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>25300</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3645,8 +3924,14 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3707,8 +3992,14 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3745,15 +4036,15 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
         <v>800</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3769,8 +4060,14 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3831,8 +4128,14 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3893,8 +4196,14 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3955,53 +4264,59 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F66" s="3">
         <v>9200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>9200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>6400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>6400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>7600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>7600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>6500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>6500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>10300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>10300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>12600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>26100</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4017,8 +4332,14 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4041,8 +4362,10 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4103,8 +4426,14 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4165,8 +4494,14 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4227,8 +4562,14 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4289,53 +4630,59 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-26700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-26700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-22600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-22600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>2600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>2600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>4300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>4300</v>
-      </c>
-      <c r="L72" s="3">
-        <v>6200</v>
-      </c>
-      <c r="M72" s="3">
-        <v>6200</v>
       </c>
       <c r="N72" s="3">
         <v>6200</v>
       </c>
       <c r="O72" s="3">
+        <v>6200</v>
+      </c>
+      <c r="P72" s="3">
+        <v>6200</v>
+      </c>
+      <c r="Q72" s="3">
         <v>36400</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4351,8 +4698,14 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4413,8 +4766,14 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4475,8 +4834,14 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4537,53 +4902,59 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F76" s="3">
         <v>10900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>10900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>14800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>14800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>39700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>39700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>42400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>42400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>43300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>43300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>45400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>79800</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4599,8 +4970,14 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4661,58 +5038,64 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4728,28 +5111,34 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-2100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-12600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-12600</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-900</v>
       </c>
       <c r="J81" s="3">
         <v>-900</v>
@@ -4758,23 +5147,23 @@
         <v>-900</v>
       </c>
       <c r="L81" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="M81" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="N81" s="3">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3">
         <v>-8700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-300</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +5179,14 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4814,16 +5209,18 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
@@ -4838,10 +5235,10 @@
         <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L83" s="3">
         <v>200</v>
@@ -4852,11 +5249,11 @@
       <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="O83" s="3">
+        <v>200</v>
+      </c>
+      <c r="P83" s="3">
+        <v>200</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
@@ -4867,17 +5264,23 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4938,8 +5341,14 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5000,8 +5409,14 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5062,8 +5477,14 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5124,8 +5545,14 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5186,53 +5613,59 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>2800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-27800</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5248,8 +5681,14 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5272,8 +5711,10 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5284,22 +5725,22 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -5308,25 +5749,25 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-800</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
@@ -5334,8 +5775,14 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5396,8 +5843,14 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5458,8 +5911,14 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5470,41 +5929,41 @@
         <v>500</v>
       </c>
       <c r="F94" s="3">
+        <v>500</v>
+      </c>
+      <c r="G94" s="3">
+        <v>500</v>
+      </c>
+      <c r="H94" s="3">
         <v>100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-500</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-2700</v>
       </c>
       <c r="N94" s="3">
         <v>-2700</v>
       </c>
       <c r="O94" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="P94" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-5700</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5520,8 +5979,14 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5544,8 +6009,10 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5582,11 +6049,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5606,8 +6073,14 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5668,8 +6141,14 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5730,8 +6209,14 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5792,53 +6277,59 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>400</v>
+      </c>
+      <c r="F100" s="3">
         <v>-300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-800</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>38500</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5854,8 +6345,14 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5872,10 +6369,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J101" s="3">
         <v>-100</v>
@@ -5890,17 +6387,17 @@
         <v>-100</v>
       </c>
       <c r="N101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P101" s="3">
         <v>-300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>700</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5916,28 +6413,34 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-700</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-200</v>
       </c>
       <c r="J102" s="3">
         <v>-200</v>
@@ -5946,23 +6449,23 @@
         <v>-200</v>
       </c>
       <c r="L102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N102" s="3">
         <v>-1500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>5700</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5976,6 +6479,12 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
